--- a/downloads/forms/self-intro.xlsx
+++ b/downloads/forms/self-intro.xlsx
@@ -551,7 +551,7 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
     </row>
-    <row r="5" ht="121.8897637795276" customHeight="1">
+    <row r="5" ht="130.3937007874016" customHeight="1">
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
@@ -568,7 +568,7 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="6" t="n"/>
     </row>
-    <row r="8" ht="121.8897637795276" customHeight="1">
+    <row r="8" ht="130.3937007874016" customHeight="1">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
@@ -585,7 +585,7 @@
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="6" t="n"/>
     </row>
-    <row r="11" ht="121.8897637795276" customHeight="1">
+    <row r="11" ht="130.3937007874016" customHeight="1">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
@@ -602,7 +602,7 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="6" t="n"/>
     </row>
-    <row r="14" ht="121.8897637795276" customHeight="1">
+    <row r="14" ht="130.3937007874016" customHeight="1">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
